--- a/Задачи_Битрикс24_портал.xlsx
+++ b/Задачи_Битрикс24_портал.xlsx
@@ -116,12 +116,12 @@
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -188,7 +188,7 @@
           <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">01.10.2026</t>
         </is>
@@ -217,7 +217,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверить Яндекс-карты на боевом домене forus.by</t>
+          <t xml:space="preserve">Проверить Яндекс-карты на домене forus.by</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -230,7 +230,7 @@
           <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19.09.2026</t>
         </is>
@@ -267,7 +267,7 @@
           <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26.09.2026</t>
         </is>
@@ -309,7 +309,7 @@
           <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26.09.2026</t>
         </is>
@@ -351,7 +351,7 @@
           <t xml:space="preserve">Александр Овчинников</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30.09.2026</t>
         </is>
@@ -388,7 +388,7 @@
           <t xml:space="preserve">Максим Александров</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26.09.2026</t>
         </is>
@@ -422,10 +422,10 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Александр Овчинников</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+          <t xml:space="preserve">Сергей Погарельский</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30.09.2026</t>
         </is>
@@ -462,7 +462,7 @@
           <t xml:space="preserve">Сергей Погарельский</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26.09.2026</t>
         </is>
@@ -496,7 +496,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Александр Овчинников</t>
+          <t xml:space="preserve">Сергей Погарельский</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Александр Овчинников</t>
+          <t xml:space="preserve">Сергей Погарельский</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -721,6 +721,11 @@
           <t xml:space="preserve">Елена Кривенко</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Светлана Бойко</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">17.10.2026</t>
@@ -760,7 +765,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Илья Драгун</t>
+          <t xml:space="preserve">Ольга Воронова</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1279,6 +1284,11 @@
           <t xml:space="preserve">Елена Кривенко</t>
         </is>
       </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Антон Закревский</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">24.10.2026</t>
@@ -1429,7 +1439,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кристина Манько</t>
+          <t xml:space="preserve">Ольга Воронова</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1469,6 +1479,11 @@
           <t xml:space="preserve">Ритта Овденко</t>
         </is>
       </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Светлана Бойко</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">15.10.2026</t>
@@ -1543,6 +1558,11 @@
           <t xml:space="preserve">Александр Овчинников</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Максим Александров</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">15.10.2026</t>
@@ -1617,6 +1637,11 @@
           <t xml:space="preserve">Илья Драгун</t>
         </is>
       </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Антон Закревский</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">15.10.2026</t>
@@ -1651,7 +1676,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Елена Кривенко</t>
+          <t xml:space="preserve">Антон Закревский</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Илья Драгун, Елена Кривенко</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1691,7 +1721,7 @@
           <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">28.10.2026</t>
         </is>
@@ -1728,9 +1758,9 @@
           <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31.10.2026</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.11.2026</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1770,9 +1800,9 @@
           <t xml:space="preserve">Антон Закревский, Илья Драгун</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31.10.2026</t>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.11.2026</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -1793,15 +1823,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1817,20 +1848,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Участок в проекте</t>
+          <t xml:space="preserve">Задач как ответственный</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Задач</t>
+          <t xml:space="preserve">Задач как соисполнитель</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Участки работ</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Первый срок</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Последний срок</t>
         </is>
@@ -1839,64 +1875,74 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Светлана Бойко</t>
+          <t xml:space="preserve">Антон Закревский</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CEO, собственник и директор</t>
+          <t xml:space="preserve">Юрисконсульт, ведёт проект</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Решения: тарифы, скидки, публикация</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.09.2026</t>
+          <t xml:space="preserve">Итоги, Макет, Проверка, Процессы</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.10.2026</t>
+          <t xml:space="preserve">19.09.2026</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.11.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Антон Закревский</t>
+          <t xml:space="preserve">Сергей Погарельский</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Юрисконсульт, ведёт проект</t>
+          <t xml:space="preserve">Дизайнер</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Макет, документооборот, правовые документы</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Данные, Проверка, Фото</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">26.09.2026</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31.10.2026</t>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.10.2026</t>
         </is>
       </c>
     </row>
@@ -1913,180 +1959,210 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Продвижение, поисковые запросы, аналитика, скоринг</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Макет, Проверка, Процессы</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">19.09.2026</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24.10.2026</t>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.11.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Елена Кривенко</t>
+          <t xml:space="preserve">Максим Александров</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Офис-менеджер, администратор портала</t>
+          <t xml:space="preserve">Руководитель технического отдела</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Данные, заявки, справочники</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.10.2026</t>
+          <t xml:space="preserve">Данные, Проверка, Фото</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.10.2026</t>
+          <t xml:space="preserve">26.09.2026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.10.2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сергей Погарельский</t>
+          <t xml:space="preserve">Елена Кривенко</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дизайнер</t>
+          <t xml:space="preserve">Офис-менеджер, администратор портала</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фотографии и оформление</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.09.2026</t>
+          <t xml:space="preserve">Данные, Процессы</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.10.2026</t>
+          <t xml:space="preserve">15.10.2026</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.10.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Максим Александров</t>
+          <t xml:space="preserve">Ритта Овденко</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Руководитель технического отдела</t>
+          <t xml:space="preserve">Главный бухгалтер</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Координаты, ревизия оборудования</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.09.2026</t>
+          <t xml:space="preserve">Проверка, Процессы</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.10.2026</t>
+          <t xml:space="preserve">15.10.2026</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.10.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Александр Овчинников</t>
+          <t xml:space="preserve">Светлана Бойко</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Специалист, дизайн и технический отдел</t>
+          <t xml:space="preserve">CEO, собственник и директор</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Съёмка, плей-листы</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.09.2026</t>
+          <t xml:space="preserve">Итоги, Макет, Проверка, Процессы</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.10.2026</t>
+          <t xml:space="preserve">26.09.2026</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.11.2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ритта Овденко</t>
+          <t xml:space="preserve">Александр Овчинников</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Главный бухгалтер</t>
+          <t xml:space="preserve">Специалист, дизайн и технический отдел</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документы, сбор за рекламу, 1С</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.10.2026</t>
+          <t xml:space="preserve">Данные, Проверка</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30.09.2026</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">24.10.2026</t>
         </is>
@@ -2105,22 +2181,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверка глазами клиента</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Проверка</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">15.10.2026</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15.10.2026</t>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.10.2026</t>
         </is>
       </c>
     </row>
@@ -2130,14 +2211,14 @@
           <t xml:space="preserve">Кристина Манько</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Старший специалист отдела продаж</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверка каталога и фильтров</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2147,86 +2228,154 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.10.2026</t>
+          <t xml:space="preserve">только как соисполнитель</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.10.2026</t>
+          <t xml:space="preserve">20.10.2026</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.10.2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:G11"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как работаем</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t xml:space="preserve">Что</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пояснение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рабочий макет портала</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.10.2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">С этого дня начинается проверка. Раньше проверять нечего.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.10.2026</t>
+          <t xml:space="preserve">Внутреннее тестирование</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Макет доведён до рабочего состояния. С этого дня начинается проверка.</t>
+          <t xml:space="preserve">октябрь – ноябрь 2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проверяем внутри компании. На общий доступ сайт не выкладываем до решения директора.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Октябрь</t>
+          <t xml:space="preserve">Все прошли свой чек-лист</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестируем внутри компании. На общий доступ сайт не выкладываем до решения директора.</t>
+          <t xml:space="preserve">15.10.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каждый проверил свой участок и записал замечания.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.10.2026</t>
+          <t xml:space="preserve">Замечания собраны в один список</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Все прошли свой чек-лист и записали замечания.</t>
+          <t xml:space="preserve">28.10.2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Антон Закревский сводит замечания и расставляет приоритеты.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.10.2026</t>
+          <t xml:space="preserve">Замечания устранены</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Светлана Бойко принимает решение: публиковать или продлить тестирование.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t xml:space="preserve">10.11.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Правки внесены, повторная проверка пройдена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Решение по публикации</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21.11.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Светлана Бойко решает: публиковать или продлить тестирование.</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -2235,6 +2384,11 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">сразу</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">В комментарий к своей задаче в Битрикс24. Не в мессенджер и не устно — иначе теряются.</t>
         </is>
       </c>
@@ -2247,7 +2401,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Столбцы совпадают с полями Битрикс24: Задача, Ответственный, Соисполнители, Крайний срок. «Что считать выполненным» — в описание задачи.</t>
+          <t xml:space="preserve">до 15.09.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Столбцы листа «Задачи» совпадают с полями Битрикс24. «Что считать выполненным» — в описание задачи.</t>
         </is>
       </c>
     </row>
@@ -2259,23 +2418,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Завести отдельную группу «Портал forus.by», чтобы задачи не смешивались с текущими.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+          <t xml:space="preserve">до 15.09.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отдельная группа «Портал forus.by», чтобы задачи не смешивались с текущими.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Рабочие файлы</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Фото_площадок_задание_дизайнеру.xlsx — что снять. Ревизия_мониторов_indoor.xlsx — простаивающее оборудование. Indoor_объекты_и_карта.xlsx — объекты с координатами.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C11"/>
 </worksheet>
 </file>
--- a/Задачи_Битрикс24_портал.xlsx
+++ b/Задачи_Битрикс24_портал.xlsx
@@ -432,7 +432,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По каждой стороне — кадр со стороны потока; по конструкции — кадр окружения</t>
+          <t xml:space="preserve">По конструкции — один кадр окружения; общие планы уже загружены</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По каждой стороне — кадр со стороны потока; по конструкции — кадр окружения</t>
+          <t xml:space="preserve">По конструкции — один кадр окружения; общие планы уже загружены</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По каждой стороне — кадр со стороны потока; по конструкции — кадр окружения</t>
+          <t xml:space="preserve">По конструкции — один кадр окружения; общие планы уже загружены</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По каждой стороне — кадр со стороны потока; по конструкции — кадр окружения</t>
+          <t xml:space="preserve">По конструкции — один кадр окружения; общие планы уже загружены</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Все 164 снимка из файла задания загружены</t>
+          <t xml:space="preserve">Все 58 снимков из файла задания загружены</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">

--- a/Задачи_Битрикс24_портал.xlsx
+++ b/Задачи_Битрикс24_портал.xlsx
@@ -338,7 +338,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверить на местности координаты 52 конструкций</t>
+          <t xml:space="preserve">Проверить на местности координаты 51 конструкции</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -358,7 +358,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отмечено, где точка на карте стоит не на конструкции</t>
+          <t xml:space="preserve">Отмечено, где точка на карте стоит не на конструкции или конструкции больше нет</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Все 58 снимков из файла задания загружены</t>
+          <t xml:space="preserve">Все 55 снимков из файла задания загружены</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
